--- a/data/2018-idealista_precio_vivienda_ccaa_norm.xlsx
+++ b/data/2018-idealista_precio_vivienda_ccaa_norm.xlsx
@@ -1,21 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iicadic-my.sharepoint.com/personal/pablo_haya_iic_uam_es/Documents/devel/periodismo-de-datos/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_ED6EFDCE8F79A8D366075C52F35B02B252058167" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52076B28-D9FB-42D9-89A2-ABDB54F93623}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>comunidad_autónoma</t>
+  </si>
+  <si>
+    <t>precio_m2_2018</t>
+  </si>
+  <si>
+    <t>comunidad_autónoma_ine</t>
+  </si>
+  <si>
+    <t>Andalucía</t>
+  </si>
+  <si>
+    <t>01 Andalucía</t>
+  </si>
+  <si>
+    <t>Aragón</t>
+  </si>
+  <si>
+    <t>02 Aragón</t>
+  </si>
+  <si>
+    <t>Asturias</t>
+  </si>
+  <si>
+    <t>03 Asturias, Principado de</t>
+  </si>
+  <si>
+    <t>Baleares</t>
+  </si>
+  <si>
+    <t>04 Balears, Illes</t>
+  </si>
+  <si>
+    <t>Canarias</t>
+  </si>
+  <si>
+    <t>05 Canarias</t>
+  </si>
+  <si>
+    <t>Cantabria</t>
+  </si>
+  <si>
+    <t>06 Cantabria</t>
+  </si>
+  <si>
+    <t>Castilla y León</t>
+  </si>
+  <si>
+    <t>07 Castilla y León</t>
+  </si>
+  <si>
+    <t>Castilla-La Mancha</t>
+  </si>
+  <si>
+    <t>08 Castilla - La Mancha</t>
+  </si>
+  <si>
+    <t>Cataluña</t>
+  </si>
+  <si>
+    <t>09 Cataluña</t>
+  </si>
+  <si>
+    <t>Ceuta</t>
+  </si>
+  <si>
+    <t>18 Ceuta</t>
+  </si>
+  <si>
+    <t>Comunitat Valenciana</t>
+  </si>
+  <si>
+    <t>10 Comunitat Valenciana</t>
+  </si>
+  <si>
+    <t>Euskadi</t>
+  </si>
+  <si>
+    <t>16 País Vasco</t>
+  </si>
+  <si>
+    <t>Extremadura</t>
+  </si>
+  <si>
+    <t>11 Extremadura</t>
+  </si>
+  <si>
+    <t>Galicia</t>
+  </si>
+  <si>
+    <t>12 Galicia</t>
+  </si>
+  <si>
+    <t>La Rioja</t>
+  </si>
+  <si>
+    <t>17 Rioja, La</t>
+  </si>
+  <si>
+    <t>Madrid Comunidad</t>
+  </si>
+  <si>
+    <t>13 Madrid, Comunidad de</t>
+  </si>
+  <si>
+    <t>Melilla</t>
+  </si>
+  <si>
+    <t>19 Melilla</t>
+  </si>
+  <si>
+    <t>Murcia Región</t>
+  </si>
+  <si>
+    <t>14 Murcia, Región de</t>
+  </si>
+  <si>
+    <t>Navarra</t>
+  </si>
+  <si>
+    <t>15 Navarra, Comunidad Foral de</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +210,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +262,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +296,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +331,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,310 +507,235 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>comunidad_autónoma</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>precio_m2_2018</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>comunidad_autónoma_ine</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Andalucía</t>
-        </is>
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>1525</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>01 Andalucía</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Aragón</t>
-        </is>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <f>1600*1.5</f>
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1288</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>02 Aragón</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Asturias</t>
-        </is>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1348</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>03 Asturias, Principado de</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Baleares</t>
-        </is>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>9</v>
       </c>
       <c r="B5">
         <v>2867</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>04 Balears, Illes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Canarias</t>
-        </is>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
       </c>
       <c r="B6">
         <v>1755</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>05 Canarias</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cantabria</t>
-        </is>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>13</v>
       </c>
       <c r="B7">
         <v>1461</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>06 Cantabria</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Castilla y León</t>
-        </is>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>15</v>
       </c>
       <c r="B8">
         <v>1167</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>07 Castilla y León</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Castilla-La Mancha</t>
-        </is>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
       </c>
       <c r="B9">
         <v>884</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>08 Castilla - La Mancha</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cataluña</t>
-        </is>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2123</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>09 Cataluña</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ceuta</t>
-        </is>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>21</v>
       </c>
       <c r="B11">
         <v>2116</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>18 Ceuta</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Comunitat Valenciana</t>
-        </is>
+      <c r="C11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12">
         <v>1336</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10 Comunitat Valenciana</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Euskadi</t>
-        </is>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>25</v>
       </c>
       <c r="B13">
         <v>2511</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>16 País Vasco</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Extremadura</t>
-        </is>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>27</v>
       </c>
       <c r="B14">
         <v>908</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>11 Extremadura</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Galicia</t>
-        </is>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>29</v>
       </c>
       <c r="B15">
         <v>1349</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>12 Galicia</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>La Rioja</t>
-        </is>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16">
         <v>1200</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>17 Rioja, La</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Madrid Comunidad</t>
-        </is>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>33</v>
       </c>
       <c r="B17">
         <v>2658</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>13 Madrid, Comunidad de</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Melilla</t>
-        </is>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>35</v>
       </c>
       <c r="B18">
         <v>1758</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>19 Melilla</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Murcia Región</t>
-        </is>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>37</v>
       </c>
       <c r="B19">
         <v>1006</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>14 Murcia, Región de</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Navarra</t>
-        </is>
+      <c r="C19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>39</v>
       </c>
       <c r="B20">
         <v>1405</v>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>15 Navarra, Comunidad Foral de</t>
-        </is>
+      <c r="C20" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
